--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/may-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/may-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -880,7 +880,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>699360-18-CM26</t>
+          <t>699360-19-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>No aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>880443249</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3696.24</v>
+        <v>4325.59</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>699360-19-CM26</t>
+          <t>4201-221-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.505.000-k</t>
+          <t>69.073.900-3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>I MUNICIPALIDAD DE CURACAVI</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>4325.59</v>
+        <v>26610.78</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4201-221-CM26</t>
+          <t>5684-256-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.073.900-3</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAVI</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>26610.78</v>
+        <v>2461.68</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>975-123-CM26</t>
+          <t>4928-38-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,22 +1078,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Solicitud de Cancelacion</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>3897.13</v>
+        <v>4617.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3675-40-CM26</t>
+          <t>1057439-3171-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,37 +1139,37 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Solicitud de Cancelacion</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.050.500-2</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PETORCA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>NETSUS SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>5770.91</v>
+        <v>1596.98</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5684-256-CM26</t>
+          <t>4856-134-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,27 +1210,27 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.160.700-3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE TIRUA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2461.68</v>
+        <v>2548.98</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4928-38-CM26</t>
+          <t>1238177-77-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>65.165.009-7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>4617.6</v>
+        <v>1031.66</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1057439-3171-CM26</t>
+          <t>3497-231-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1332,27 +1332,27 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1596.98</v>
+        <v>1056.72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1238177-77-CM26</t>
+          <t>1020-136-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1388,17 +1388,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>65.165.009-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1031.66</v>
+        <v>2579.15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4856-134-CM26</t>
+          <t>1351461-18-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1454,27 +1454,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.160.700-3</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIRUA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2548.98</v>
+        <v>26155.37</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3497-231-CM26</t>
+          <t>872-222-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,17 +1515,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>82.983.100-7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>COMISION CHILENA DE ENERGIA NUCLEAR</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1056.72</v>
+        <v>8453.76</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1351461-18-CM26</t>
+          <t>2404-577-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,37 +1566,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>26155.37</v>
+        <v>34026.38</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1020-136-CM26</t>
+          <t>3507-326-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,27 +1637,27 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>65.321.890-7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Departamento de Salud</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2579.15</v>
+        <v>17740.52</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>872-222-CM26</t>
+          <t>1018-58-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1693,17 +1693,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>82.983.100-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>COMISION CHILENA DE ENERGIA NUCLEAR</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>8453.76</v>
+        <v>55977.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2404-577-CM26</t>
+          <t>2678-71-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1759,27 +1759,27 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>34026.38</v>
+        <v>4878.64</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3507-326-CM26</t>
+          <t>606-161-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,37 +1810,37 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>65.321.890-7</t>
+          <t>60.513.000-3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>17740.52</v>
+        <v>60154.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1018-58-CM26</t>
+          <t>577290-48-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,22 +1871,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.979.750-7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Subsecretaria de Transportes</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>880443249</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>55977.6</v>
+        <v>4226.88</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2678-71-CM26</t>
+          <t>3864-105-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>4878.64</v>
+        <v>18462.61</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>606-161-CM26</t>
+          <t>2069-4322-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>60.513.000-3</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>60154.5</v>
+        <v>1031.66</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>577290-48-CM26</t>
+          <t>624-74-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2064,27 +2064,27 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.979.750-7</t>
+          <t>72.225.700-6</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Subsecretaria de Transportes</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>4226.88</v>
+        <v>70089.22</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3864-105-CM26</t>
+          <t>4238-132-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2120,22 +2120,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>69.160.202-8</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>Ilustre Municipalidad de Curanilahue - Salud</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>18462.61</v>
+        <v>19514.57</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2069-4322-CM26</t>
+          <t>1233616-932-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2186,27 +2186,27 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>Servicio Local de Educación Pública Punilla Cordil</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>NETSUS SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1031.66</v>
+        <v>12195.12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>624-74-CM26</t>
+          <t>2450-536-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>72.225.700-6</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>70089.22</v>
+        <v>33398.14</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4238-132-CM26</t>
+          <t>3838-123-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,27 +2308,27 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.160.202-8</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Curanilahue - Salud</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>19514.57</v>
+        <v>4226.88</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1233616-932-CM26</t>
+          <t>1393-250-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,22 +2359,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>12195.12</v>
+        <v>8255.860000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1393-250-CM26</t>
+          <t>2483-191-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2430,27 +2430,27 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>69.071.300-4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>I MUNICIPALIDAD DE QUILICURA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>8255.860000000001</v>
+        <v>61542.04</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3838-123-CM26</t>
+          <t>557639-614-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>71.014.200-9</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>4226.88</v>
+        <v>1479.41</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2450-536-CM26</t>
+          <t>1622-657-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,27 +2552,27 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>79.770.640-k</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>33398.14</v>
+        <v>1123.87</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>557639-614-CM26</t>
+          <t>14-190-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,37 +2603,37 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>71.014.200-9</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1479.41</v>
+        <v>2797.74</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2483-191-CM26</t>
+          <t>14-188-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,22 +2664,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.071.300-4</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILICURA</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>61542.04</v>
+        <v>13638.97</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1622-657-CM26</t>
+          <t>14-187-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2735,27 +2735,27 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>79.770.640-k</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1123.87</v>
+        <v>17485.86</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>14-190-CM26</t>
+          <t>14-189-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2797.74</v>
+        <v>3497.17</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>14-188-CM26</t>
+          <t>14-185-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>13638.97</v>
+        <v>3846.89</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>14-187-CM26</t>
+          <t>1078326-3-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2918,27 +2918,27 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>60.605.000-3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>INSTITUTO ANTARTICO CHILENO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>17485.86</v>
+        <v>4960.8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>14-189-CM26</t>
+          <t>577290-45-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.979.750-7</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>Subsecretaria de Transportes</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>79.770.640-k</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>3497.17</v>
+        <v>2579.33</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>14-185-CM26</t>
+          <t>14-186-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>3846.89</v>
+        <v>17602.43</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1078326-3-CM26</t>
+          <t>976-81-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,27 +3101,27 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>60.605.000-3</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>INSTITUTO ANTARTICO CHILENO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>4960.8</v>
+        <v>69725.08</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>577290-45-CM26</t>
+          <t>4079-211-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,27 +3162,27 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.979.750-7</t>
+          <t>69.151.000-k</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Subsecretaria de Transportes</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>79.770.640-k</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2579.33</v>
+        <v>7819.73</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>14-186-CM26</t>
+          <t>577290-47-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.979.750-7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>Subsecretaria de Transportes</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>NETSUS SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>17602.43</v>
+        <v>999.6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>976-81-CM26</t>
+          <t>1057544-9434-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,37 +3274,37 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.607.202-1</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO DE SALUD DE TALCAHUANO HOSPITAL</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>69725.08</v>
+        <v>1203.6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4079-211-CM26</t>
+          <t>188-371-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3335,37 +3335,37 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.151.000-k</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>79.770.640-k</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>7819.73</v>
+        <v>17002.6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>577290-47-CM26</t>
+          <t>840405-21-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3396,37 +3396,37 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.979.750-7</t>
+          <t>69.110.700-0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Subsecretaria de Transportes</t>
+          <t>I MUNICIPALIDAD DE RIO CLARO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>999.6</v>
+        <v>10644.31</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1057544-9434-CM26</t>
+          <t>2594-437-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,27 +3467,27 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.607.202-1</t>
+          <t>73.568.600-3</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE TALCAHUANO HOSPITAL</t>
+          <t>I MUNICIPALIDAD DE CONCON</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1203.6</v>
+        <v>2113.44</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>188-371-CM26</t>
+          <t>3885-205-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,37 +3518,37 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>79.770.640-k</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>17002.6</v>
+        <v>8255.860000000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>840405-21-CM26</t>
+          <t>3885-206-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3584,22 +3584,22 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.110.700-0</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO CLARO</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>10644.31</v>
+        <v>8255.860000000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3807-210-CM26</t>
+          <t>1051173-51-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,37 +3640,37 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Cancelada por Comprador</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.120.200-3</t>
+          <t>60.100.003-2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EMPEDRADO</t>
+          <t>MINISTERIO SECRETARIA GENERAL DE LA PRESIDENCIA DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>NextTime Software S.A.</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>99.576.370-2</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>802.9299999999999</v>
+        <v>74403.8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3885-206-CM26</t>
+          <t>1078326-4-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,17 +3711,17 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>60.605.000-3</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>INSTITUTO ANTARTICO CHILENO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>8255.860000000001</v>
+        <v>1538.55</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3885-205-CM26</t>
+          <t>14-195-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,27 +3772,27 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>8255.860000000001</v>
+        <v>785.4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2594-437-CM26</t>
+          <t>1261-28-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,27 +3833,27 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>73.568.600-3</t>
+          <t>61.923.200-3</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCON</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2113.44</v>
+        <v>14794.08</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1051173-51-CM26</t>
+          <t>1020-162-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>60.100.003-2</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>MINISTERIO SECRETARIA GENERAL DE LA PRESIDENCIA DE LA REPUBLICA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>74403.8</v>
+        <v>656393.34</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1078326-4-CM26</t>
+          <t>229-384-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,37 +3945,37 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>60.605.000-3</t>
+          <t>69.141.100-1</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>INSTITUTO ANTARTICO CHILENO</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1538.55</v>
+        <v>10338.72</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>14-195-CM26</t>
+          <t>3827-320-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>69.261.400-3</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>785.4</v>
+        <v>12495</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1261-28-CM26</t>
+          <t>907562-59-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,37 +4067,37 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.923.200-3</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>14794.08</v>
+        <v>8426.75</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1020-162-CM26</t>
+          <t>552975-308-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.070.301-7</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP DE DESARROLLO SOCIAL DE PROVIDENCIA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>880443249</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>656393.3376</v>
+        <v>66260.84</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2566-164-CM26</t>
+          <t>2341-226-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,37 +4189,37 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>No aceptada</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.090.700-3</t>
+          <t>69.072.700-5</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHEPICA</t>
+          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>780.3099999999999</v>
+        <v>39217.54</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>229-384-CM26</t>
+          <t>568658-841-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,27 +4250,27 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.141.100-1</t>
+          <t>70.872.300-2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COIHUECO</t>
+          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>10338.72</v>
+        <v>3170.16</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3827-320-CM26</t>
+          <t>1084156-411-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,27 +4321,27 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.261.400-3</t>
+          <t>65.181.672-6</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA ANDALIEN SUR</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>NETSUS SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>12495</v>
+        <v>9346.26</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>552975-308-CM26</t>
+          <t>705290-1047-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4372,22 +4372,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.070.301-7</t>
+          <t>61.608.205-1</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>CORP DE DESARROLLO SOCIAL DE PROVIDENCIA</t>
+          <t>SERVICIO SALUD OCCIDENTE HOSPITAL DR FELIX BULNES CERDA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>66260.84</v>
+        <v>44351.3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>907562-59-CM26</t>
+          <t>2793-487-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4433,27 +4433,27 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>Iluste Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4466,323 +4466,18 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>8426.75</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>705290-1047-CM26</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>may-2026</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>61.608.205-1</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>SERVICIO SALUD OCCIDENTE HOSPITAL DR FELIX BULNES CERDA</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>TECNOLOGIA BS SPA</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="n">
-        <v>44351.3</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2341-226-CM26</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>may-2026</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>69.072.700-5</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>76.334.381-2</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="n">
-        <v>39217.54</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>568658-841-CM26</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>may-2026</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>70.872.300-2</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="n">
-        <v>3170.16</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>1084156-411-CM26</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>may-2026</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>65.181.672-6</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA ANDALIEN SUR</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Bío-Bío</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>NETSUS SPA</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>76.288.338-4</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="n">
-        <v>9346.26</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2793-487-CM26</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>may-2026</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>69.255.400-0</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>TECNOLOGIA BS SPA</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="n">
-        <v>402884.496</v>
+        <v>402884.5</v>
       </c>
     </row>
   </sheetData>
